--- a/utils/monday_sprint_sprint_2025-1.xlsx
+++ b/utils/monday_sprint_sprint_2025-1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="172">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>29273</t>
+    <t>8088954527</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>19/12/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>12/01/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,13 +102,13 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>29248</t>
+    <t>8088973042</t>
   </si>
   <si>
     <t>Alterações IROG Usinagem</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>8060398495</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -123,7 +123,10 @@
     <t>16/12/2024</t>
   </si>
   <si>
-    <t>28410</t>
+    <t>11/01/2025</t>
+  </si>
+  <si>
+    <t>8009536722</t>
   </si>
   <si>
     <t>ENDEREÇAMENTO ALMOXARIFADO</t>
@@ -135,7 +138,7 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>29184</t>
+    <t>8092807089</t>
   </si>
   <si>
     <t>Ensaio de peça seriada e RX está sendo criado na etapa errada</t>
@@ -144,31 +147,40 @@
     <t>20/12/2024</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>8094898732</t>
   </si>
   <si>
     <t>Habilitar Tela eventos financeiros para Sueli - Julius - Entrega</t>
   </si>
   <si>
-    <t>28135</t>
+    <t>13/01/2025</t>
+  </si>
+  <si>
+    <t>8009612085</t>
   </si>
   <si>
     <t>Apontamento de moldagem USE - Máquina</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>8095676927</t>
   </si>
   <si>
     <t>Ambiente de testes controle da pátio</t>
   </si>
   <si>
-    <t>26389</t>
+    <t>8095030582</t>
   </si>
   <si>
     <t>Controle Automático de n° sequencial de peça para ID de Bruto</t>
   </si>
   <si>
-    <t>29139</t>
+    <t>07/01/2025</t>
+  </si>
+  <si>
+    <t>8071649895</t>
   </si>
   <si>
     <t>Melhoria de relatório</t>
@@ -177,121 +189,136 @@
     <t>17/12/2024</t>
   </si>
   <si>
-    <t>29315</t>
+    <t>29/12/2024</t>
+  </si>
+  <si>
+    <t>8088728247</t>
   </si>
   <si>
     <t>Indicadores GIQ</t>
   </si>
   <si>
-    <t>29298</t>
+    <t>02/01/2025</t>
+  </si>
+  <si>
+    <t>8088854158</t>
   </si>
   <si>
     <t>BUG - Inventário Consignado Almoxarifado</t>
   </si>
   <si>
-    <t>29274</t>
+    <t>8088911751</t>
   </si>
   <si>
     <t>ALTERAR ORDEM DOS CAMPOS</t>
   </si>
   <si>
-    <t>29247</t>
+    <t>8088988040</t>
   </si>
   <si>
     <t>Apontamento Ajustagem</t>
   </si>
   <si>
-    <t>29236</t>
+    <t>8089001741</t>
   </si>
   <si>
     <t>[ALEA - ALTONA] Meeting revisão sistema</t>
   </si>
   <si>
-    <t>29214</t>
+    <t>8089046848</t>
   </si>
   <si>
     <t>PENDÊNCIA COMPRA/CONSERTO DE MODELO</t>
   </si>
   <si>
-    <t>29213</t>
+    <t>8089089345</t>
   </si>
   <si>
     <t>OBSERVAÇÃO DE SEQUÊNCIA RELACIONADA</t>
   </si>
   <si>
-    <t>29212</t>
+    <t>8089099318</t>
   </si>
   <si>
     <t>BOTÃO VISUALIZAR PENDÊNCIAS</t>
   </si>
   <si>
-    <t>29211</t>
+    <t>8089109077</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO FLUXO 108 E 110</t>
   </si>
   <si>
-    <t>29198</t>
+    <t>26/12/2024</t>
+  </si>
+  <si>
+    <t>8089139783</t>
   </si>
   <si>
     <t>Apontamento Inspeção</t>
   </si>
   <si>
-    <t>29193</t>
+    <t>22/12/2024</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>8089194143</t>
   </si>
   <si>
     <t>APONTAMENTO TABLET MANIPULADOR</t>
   </si>
   <si>
-    <t>29192</t>
+    <t>8089210936</t>
   </si>
   <si>
     <t>Habilitar ctrl C ctrl V</t>
   </si>
   <si>
-    <t>29186</t>
+    <t>8092794767</t>
   </si>
   <si>
     <t>Acrescentar mais não conformidades ao sistema</t>
   </si>
   <si>
-    <t>29173</t>
+    <t>8092812535</t>
   </si>
   <si>
     <t>CÓPIA DE INFORMAÇÕES NA TELA DOCUMENTAÇÃO CLIENT</t>
   </si>
   <si>
-    <t>29172</t>
+    <t>8092820958</t>
   </si>
   <si>
     <t>SETOR PRÉ-PRODUTIVO DE REUNIÃO RATPP/PFMEA</t>
   </si>
   <si>
-    <t>29162</t>
+    <t>8092827855</t>
   </si>
   <si>
     <t>Melhoria Informações Setor 610 / 611</t>
   </si>
   <si>
-    <t>29156</t>
+    <t>8092859766</t>
   </si>
   <si>
     <t>Sistema de corridas - Fechamento Materiais</t>
   </si>
   <si>
-    <t>29135</t>
+    <t>8092897613</t>
   </si>
   <si>
     <t>CVM - Inclusão de campos</t>
   </si>
   <si>
-    <t>29130</t>
+    <t>8092907317</t>
   </si>
   <si>
     <t>Cadastro na CPP</t>
   </si>
   <si>
-    <t>29319</t>
+    <t>8092943625</t>
   </si>
   <si>
     <t>Correção</t>
@@ -300,25 +327,25 @@
     <t>Não esta trocando o nome do ativo</t>
   </si>
   <si>
-    <t>29231</t>
+    <t>8092951904</t>
   </si>
   <si>
     <t>Inclusão Cat France atualização EDI - Fechar Chamado</t>
   </si>
   <si>
-    <t>29138</t>
+    <t>8095064879</t>
   </si>
   <si>
     <t>Cálculo NF de importação - Validação</t>
   </si>
   <si>
-    <t>29032</t>
+    <t>8095110336</t>
   </si>
   <si>
     <t>Projeto - Sequencias Críticas -</t>
   </si>
   <si>
-    <t>29325</t>
+    <t>8102759299</t>
   </si>
   <si>
     <t>Ordem de Compra - integração Benner</t>
@@ -330,6 +357,9 @@
     <t>Semana 4</t>
   </si>
   <si>
+    <t>8189058901</t>
+  </si>
+  <si>
     <t>Alterar o filtro para quando for ano comercial, por exemplo. Selecionar "2024", mostrar de out/2023 a set/2024</t>
   </si>
   <si>
@@ -339,28 +369,49 @@
     <t>Janeiro</t>
   </si>
   <si>
+    <t>8189060385</t>
+  </si>
+  <si>
     <t>Na tela "ManutençãoIndicadoresArea", salvar filtros em variáveis de sessão</t>
   </si>
   <si>
+    <t>8189061824</t>
+  </si>
+  <si>
     <t>Muitas falhas ao transitar entre os gráficos e anos no dashboard, muitas vezes o gráfico só carrega depois de atualizar a página (Setor PCPP não carrega nenhum gráfico</t>
   </si>
   <si>
+    <t>8189063320</t>
+  </si>
+  <si>
     <t>Colocar o valor da meta junto com a legenda do gráfico, exemplo</t>
   </si>
   <si>
+    <t>8189064348</t>
+  </si>
+  <si>
     <t>Trocar a cor de fundo do sinaleiro, atualmente ele está preto, colocar branco</t>
   </si>
   <si>
+    <t>8189065162</t>
+  </si>
+  <si>
     <t>No Dashboard, colocar o acumulado de três anos anteriores ao invés de dois</t>
   </si>
   <si>
+    <t>8189068329</t>
+  </si>
+  <si>
     <t>Função de voltar para a página que eu estava, exemplo: quando eu estiver alimentando um indicador da pág.3 e salvar, gostaria de voltar para a página três e não para o início;</t>
   </si>
   <si>
+    <t>8189069492</t>
+  </si>
+  <si>
     <t>Se possível, colocar um gatilho quando um plano de ação estiver chegando perto da data de término.</t>
   </si>
   <si>
-    <t>29402</t>
+    <t>8200628838</t>
   </si>
   <si>
     <t>OTF 161790 não aparece prazo de entrega no Planilhão</t>
@@ -369,13 +420,13 @@
     <t>09/01/2025</t>
   </si>
   <si>
-    <t>29170</t>
+    <t>8060334367</t>
   </si>
   <si>
     <t>Melhorias apontamento de solda</t>
   </si>
   <si>
-    <t>29293</t>
+    <t>8088884879</t>
   </si>
   <si>
     <t>MELHORIAS APONTAMENTO MANIPULADOR PEQUENO</t>
@@ -390,7 +441,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-1</t>
+    <t>Dez/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -441,7 +492,7 @@
     <t>Muito Alta</t>
   </si>
   <si>
-    <t>Sim</t>
+    <t>Semana 1</t>
   </si>
   <si>
     <t>A fazer</t>
@@ -457,6 +508,9 @@
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Não definida</t>
@@ -1082,7 +1136,7 @@
         <v>35</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1099,7 +1153,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1111,10 +1165,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1126,7 +1180,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1138,7 +1192,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1146,7 +1200,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1158,10 +1212,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1173,10 +1227,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1193,7 +1247,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1205,10 +1259,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -1220,10 +1274,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1240,7 +1294,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1252,10 +1306,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -1267,10 +1321,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1279,7 +1333,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1287,7 +1341,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1299,10 +1353,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1314,10 +1368,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1334,7 +1388,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1346,10 +1400,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -1361,10 +1415,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1381,7 +1435,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1393,10 +1447,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -1408,10 +1462,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1428,7 +1482,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1440,10 +1494,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1458,7 +1512,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1475,7 +1529,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1487,10 +1541,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1505,7 +1559,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1522,7 +1576,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1534,10 +1588,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1552,7 +1606,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1569,7 +1623,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1581,10 +1635,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1599,7 +1653,7 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1616,7 +1670,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1628,10 +1682,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1646,7 +1700,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1663,7 +1717,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1675,10 +1729,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1693,7 +1747,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1710,7 +1764,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1722,10 +1776,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1740,7 +1794,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1757,7 +1811,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1769,10 +1823,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1787,7 +1841,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1804,7 +1858,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1816,10 +1870,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1834,7 +1888,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1851,7 +1905,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1863,10 +1917,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1881,13 +1935,13 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>27</v>
@@ -1898,7 +1952,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1910,10 +1964,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1928,7 +1982,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1945,7 +1999,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1957,10 +2011,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1975,7 +2029,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1992,7 +2046,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2004,10 +2058,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2019,16 +2073,16 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>27</v>
@@ -2039,7 +2093,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2051,10 +2105,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2066,10 +2120,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2086,7 +2140,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2098,10 +2152,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2113,10 +2167,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2133,7 +2187,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2145,10 +2199,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2160,10 +2214,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2180,7 +2234,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2192,10 +2246,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2207,10 +2261,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2227,7 +2281,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2239,10 +2293,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2254,10 +2308,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2274,7 +2328,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2286,10 +2340,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2301,10 +2355,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2321,22 +2375,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2348,10 +2402,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2368,7 +2422,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2380,10 +2434,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2395,16 +2449,16 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>27</v>
@@ -2415,7 +2469,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2427,10 +2481,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2442,10 +2496,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2462,7 +2516,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2474,10 +2528,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2489,10 +2543,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2509,7 +2563,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2521,10 +2575,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2536,10 +2590,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2548,7 +2602,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2556,38 +2610,38 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
       </c>
@@ -2595,46 +2649,46 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
       </c>
@@ -2642,46 +2696,46 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
       </c>
@@ -2689,46 +2743,46 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K39" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
       </c>
@@ -2736,46 +2790,46 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K40" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
       </c>
@@ -2783,46 +2837,46 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K41" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
       </c>
@@ -2830,46 +2884,46 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
       </c>
@@ -2877,46 +2931,46 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
       </c>
@@ -2924,30 +2978,30 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -2959,42 +3013,42 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O44" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>34</v>
@@ -3009,7 +3063,7 @@
         <v>35</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3026,7 +3080,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3038,10 +3092,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3056,10 +3110,10 @@
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>26</v>
@@ -3084,23 +3138,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3108,16 +3162,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3125,10 +3179,10 @@
         <v>45</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3136,7 +3190,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3149,7 +3203,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -3157,7 +3211,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3188,12 +3242,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B2">
         <v>45</v>
@@ -3201,13 +3255,13 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3217,25 +3271,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3252,16 +3306,16 @@
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -3270,10 +3324,10 @@
         <v>44</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="Q10">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3293,24 +3347,24 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q11">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3322,47 +3376,53 @@
         <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Q12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
+      <c r="P13" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -3370,7 +3430,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3378,7 +3438,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3386,7 +3446,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3394,10 +3454,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3405,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3413,142 +3473,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
